--- a/output/pdf_financials_xlsx/BFM.xlsx
+++ b/output/pdf_financials_xlsx/BFM.xlsx
@@ -4629,25 +4629,25 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>0.561914</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.6767919999999999</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.6936020000000001</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>0.6936020000000001</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>0.709307</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>0.709307</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>0.709307</v>
       </c>
       <c r="I92" s="1" t="inlineStr">
         <is>
@@ -4655,16 +4655,16 @@
         </is>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>1.388754</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>1.693238</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>0.7825569999999999</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>2.437721</v>
       </c>
     </row>
     <row r="93">
@@ -5760,7 +5760,7 @@
         <v>0</v>
       </c>
       <c r="K118" s="3" t="n">
-        <v>0</v>
+        <v>-0.0015</v>
       </c>
       <c r="L118" s="3" t="n">
         <v>-0.175775</v>
@@ -7596,7 +7596,11 @@
           <t>Reserves 6</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
           <t>-</t>
@@ -8888,7 +8892,11 @@
           <t>Reserves (note 6)</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr"/>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E31" t="inlineStr">
         <is>
           <t>-</t>
@@ -9660,7 +9668,11 @@
           <t>Reserves (note 5)</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr"/>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E41" t="inlineStr">
         <is>
           <t>-</t>
@@ -10504,7 +10516,11 @@
           <t>Reserves (Note 5)</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr"/>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E52" t="inlineStr">
         <is>
           <t>-</t>
@@ -10964,7 +10980,11 @@
           <t>Reserves (Note 5)</t>
         </is>
       </c>
-      <c r="D58" t="inlineStr"/>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E58" t="inlineStr">
         <is>
           <t>-</t>
@@ -11880,7 +11900,11 @@
           <t>Reserves (Note 6)</t>
         </is>
       </c>
-      <c r="D70" t="inlineStr"/>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E70" t="inlineStr">
         <is>
           <t>-</t>
@@ -13076,7 +13100,11 @@
           <t>Reserves 7</t>
         </is>
       </c>
-      <c r="D86" t="inlineStr"/>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E86" s="5" t="n">
         <v>0.561914</v>
       </c>
@@ -15954,7 +15982,11 @@
           <t>Exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D124" t="inlineStr"/>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E124" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/BFM.xlsx
+++ b/output/pdf_financials_xlsx/BFM.xlsx
@@ -895,10 +895,10 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.002099</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.000563</v>
       </c>
       <c r="D12" s="3" t="n">
         <v>0</v>
@@ -924,13 +924,13 @@
         <v>0</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>0.001056</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>0.082842</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0</v>
+        <v>0.065244</v>
       </c>
     </row>
     <row r="13">
@@ -1616,10 +1616,10 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-1.71247</v>
+        <v>-1.714569</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-1.948792</v>
+        <v>-1.949355</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>-1.278126</v>
@@ -1645,13 +1645,13 @@
         <v>-0.607919</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-0.577425</v>
+        <v>-0.578481</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>-1.491743</v>
+        <v>-1.574585</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>-1.197973</v>
+        <v>-1.263217</v>
       </c>
     </row>
     <row r="28">
@@ -1706,10 +1706,10 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-1.71247</v>
+        <v>-1.714569</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-1.948792</v>
+        <v>-1.949355</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>-1.278126</v>
@@ -1735,13 +1735,13 @@
         <v>-0.607919</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-0.577425</v>
+        <v>-0.578481</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-1.491743</v>
+        <v>-1.574585</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-1.197973</v>
+        <v>-1.263217</v>
       </c>
     </row>
     <row r="30">
@@ -1949,13 +1949,13 @@
         <v>0.003017</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.624674</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.023875</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.021995</v>
       </c>
       <c r="I34" s="1" t="inlineStr">
         <is>
@@ -1963,16 +1963,16 @@
         </is>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.106987</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.061027</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.378742</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>2.155638</v>
       </c>
     </row>
     <row r="35">
@@ -2039,13 +2039,13 @@
         <v>0.016847</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.624674</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.023875</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.021995</v>
       </c>
       <c r="I36" s="1" t="inlineStr">
         <is>
@@ -2053,16 +2053,16 @@
         </is>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.106987</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.061027</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>4.77</v>
+        <v>5.148742</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>2.155638</v>
       </c>
     </row>
     <row r="37">
@@ -2579,13 +2579,13 @@
         <v>0</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.624674</v>
+        <v>0</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.023875</v>
+        <v>0</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.021995</v>
+        <v>0</v>
       </c>
       <c r="I48" s="1" t="inlineStr">
         <is>
@@ -2593,16 +2593,16 @@
         </is>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.106987</v>
+        <v>0</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.061027</v>
+        <v>0</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.378742</v>
+        <v>0</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>2.156216</v>
+        <v>0.000578</v>
       </c>
     </row>
     <row r="49">
@@ -6660,7 +6660,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -7910,7 +7910,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -21186,7 +21186,7 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
@@ -25166,7 +25166,7 @@
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E247" t="inlineStr">
@@ -26744,7 +26744,7 @@
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E268" s="5" t="n">
